--- a/student_data.xlsx
+++ b/student_data.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR4"/>
+  <dimension ref="A1:AR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.44140625" customWidth="1" min="1" max="1"/>
@@ -701,222 +701,222 @@
       </c>
     </row>
     <row r="2" customFormat="1" s="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>BOPPUDI SANTHOSH</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>24B21A4241</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>AIML</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>8309224358</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>395484533771</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>B VENKATSWARA RAO</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>647521027403</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>INTERMEDIATE</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>BUSINESS</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>8332898685</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>BOPPUDI JYOTHI</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>-----</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>-----</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>----</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>BC- B</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>KUMMARA</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>INTERMIDIEATE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>90772070640</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>80400</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>202413724418</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>2413221789</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>SRI  CHAITHANYA</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>VIJAYAWADA</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NTR </t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>89.6%</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>2212116114</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>PRAGATHI NIKETAN</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>GANGUR VIJAYAWADA</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>KRISHNA</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>SSC</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AH2" s="2" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>INDIAN</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AK2" s="2" t="inlineStr">
         <is>
           <t>8-115</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>VANUKURU ROAD</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>PENAMALURU</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>KRISHNA</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>KRISHNA</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
         <is>
           <t>521139</t>
         </is>
@@ -925,12 +925,12 @@
     <row r="3" customFormat="1" s="2">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boppudi santhosh</t>
+          <t>s</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24B21A4429</t>
+          <t>s</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -938,26 +938,23 @@
           <t>AID</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sSs</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>s</t>
@@ -973,11 +970,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>s</t>
@@ -988,11 +981,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>s</t>
@@ -1139,224 +1128,7 @@
         </is>
       </c>
     </row>
-    <row r="4" customFormat="1" s="2">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>22345678a</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AIML</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-    </row>
+    <row r="4" customFormat="1" s="2"/>
     <row r="5" customFormat="1" s="2"/>
     <row r="6" customFormat="1" s="2"/>
     <row r="7" customFormat="1" s="2"/>

--- a/student_data.xlsx
+++ b/student_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -433,49 +433,49 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AR3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24.44140625" customWidth="1" min="1" max="1"/>
-    <col width="22.21875" customWidth="1" min="2" max="3"/>
-    <col width="26.33203125" customWidth="1" min="4" max="4"/>
-    <col width="27.88671875" customWidth="1" min="5" max="5"/>
-    <col width="30.33203125" customWidth="1" min="6" max="6"/>
+    <col width="24.42578125" customWidth="1" min="1" max="1"/>
+    <col width="22.28515625" customWidth="1" min="2" max="3"/>
+    <col width="26.28515625" customWidth="1" min="4" max="4"/>
+    <col width="27.85546875" customWidth="1" min="5" max="5"/>
+    <col width="30.28515625" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28.77734375" customWidth="1" min="8" max="8"/>
-    <col width="29.5546875" customWidth="1" min="9" max="9"/>
+    <col width="28.7109375" customWidth="1" min="8" max="8"/>
+    <col width="29.5703125" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="19.77734375" customWidth="1" min="11" max="11"/>
-    <col width="20.21875" customWidth="1" min="12" max="12"/>
-    <col width="21.44140625" customWidth="1" min="13" max="13"/>
-    <col width="27.44140625" customWidth="1" min="14" max="14"/>
-    <col width="25.6640625" customWidth="1" min="15" max="15"/>
+    <col width="19.7109375" customWidth="1" min="11" max="11"/>
+    <col width="20.28515625" customWidth="1" min="12" max="12"/>
+    <col width="21.42578125" customWidth="1" min="13" max="13"/>
+    <col width="27.42578125" customWidth="1" min="14" max="14"/>
+    <col width="25.7109375" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="17.33203125" customWidth="1" min="17" max="17"/>
-    <col width="22.5546875" customWidth="1" min="18" max="18"/>
-    <col width="27.33203125" customWidth="1" min="19" max="19"/>
-    <col width="29.77734375" customWidth="1" min="20" max="20"/>
-    <col width="18.33203125" customWidth="1" min="21" max="21"/>
-    <col width="28.6640625" customWidth="1" min="22" max="23"/>
-    <col width="38.44140625" customWidth="1" min="24" max="24"/>
-    <col width="32.88671875" customWidth="1" min="25" max="25"/>
-    <col width="27.21875" customWidth="1" min="26" max="26"/>
-    <col width="20.109375" customWidth="1" min="27" max="27"/>
-    <col width="16.88671875" customWidth="1" min="28" max="28"/>
-    <col width="17.88671875" customWidth="1" min="29" max="29"/>
+    <col width="17.28515625" customWidth="1" min="17" max="17"/>
+    <col width="22.5703125" customWidth="1" min="18" max="18"/>
+    <col width="27.28515625" customWidth="1" min="19" max="19"/>
+    <col width="29.7109375" customWidth="1" min="20" max="20"/>
+    <col width="18.28515625" customWidth="1" min="21" max="21"/>
+    <col width="28.7109375" customWidth="1" min="22" max="23"/>
+    <col width="38.42578125" customWidth="1" min="24" max="24"/>
+    <col width="32.85546875" customWidth="1" min="25" max="25"/>
+    <col width="27.28515625" customWidth="1" min="26" max="26"/>
+    <col width="20.140625" customWidth="1" min="27" max="27"/>
+    <col width="16.85546875" customWidth="1" min="28" max="28"/>
+    <col width="17.85546875" customWidth="1" min="29" max="29"/>
     <col width="35" customWidth="1" min="30" max="30"/>
     <col width="24" customWidth="1" min="31" max="31"/>
-    <col width="18.33203125" customWidth="1" min="32" max="33"/>
+    <col width="18.28515625" customWidth="1" min="32" max="33"/>
     <col width="16" customWidth="1" min="34" max="34"/>
-    <col width="16.109375" customWidth="1" min="35" max="35"/>
-    <col width="18.6640625" customWidth="1" min="36" max="36"/>
-    <col width="15.5546875" customWidth="1" min="37" max="37"/>
+    <col width="16.140625" customWidth="1" min="35" max="35"/>
+    <col width="18.7109375" customWidth="1" min="36" max="36"/>
+    <col width="15.5703125" customWidth="1" min="37" max="37"/>
     <col width="25" customWidth="1" min="38" max="38"/>
-    <col width="19.77734375" customWidth="1" min="39" max="39"/>
-    <col width="19.44140625" customWidth="1" min="40" max="40"/>
-    <col width="20.77734375" customWidth="1" min="41" max="41"/>
-    <col width="23.6640625" customWidth="1" min="42" max="42"/>
-    <col width="21.88671875" customWidth="1" min="43" max="43"/>
-    <col width="17.109375" customWidth="1" min="44" max="44"/>
+    <col width="19.7109375" customWidth="1" min="39" max="39"/>
+    <col width="19.42578125" customWidth="1" min="40" max="40"/>
+    <col width="20.7109375" customWidth="1" min="41" max="41"/>
+    <col width="23.7109375" customWidth="1" min="42" max="42"/>
+    <col width="21.85546875" customWidth="1" min="43" max="43"/>
+    <col width="17.140625" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="1">
@@ -925,206 +925,222 @@
     <row r="3" customFormat="1" s="2">
       <c r="A3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>RAJANLA CHARAN TEJA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>24B21A4240</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AID</t>
+          <t>AIML</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>9701691848</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>781825104022</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RAJANALA SUBBARAO</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ss</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>-------</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>FARMER</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>9640490368</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>RAJANAL JYOTHI</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>------------------------</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>TYLER</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>-----------------</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>8106810449</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>OC</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>KAPU</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>INTER</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>---</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>----</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>---</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>---</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>-\</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>--</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2347,6 @@
     <row r="1204" customFormat="1" s="2"/>
     <row r="1205" customFormat="1" s="2"/>
     <row r="1206" customFormat="1" s="2"/>
-    <row r="1207" customFormat="1" s="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
